--- a/DCAT/dcat_profile_coverage.xlsx
+++ b/DCAT/dcat_profile_coverage.xlsx
@@ -9200,7 +9200,11 @@
           <t>odrs:RightsStatement</t>
         </is>
       </c>
-      <c r="C236" s="2" t="inlineStr"/>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D236" s="3" t="inlineStr"/>
       <c r="E236" s="3" t="inlineStr"/>
       <c r="F236" s="3" t="inlineStr"/>
@@ -9228,7 +9232,11 @@
           <t>odrs:RightsStatement</t>
         </is>
       </c>
-      <c r="C237" s="2" t="inlineStr"/>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D237" s="3" t="inlineStr"/>
       <c r="E237" s="3" t="inlineStr"/>
       <c r="F237" s="3" t="inlineStr"/>
@@ -9256,7 +9264,11 @@
           <t>odrs:RightsStatement</t>
         </is>
       </c>
-      <c r="C238" s="2" t="inlineStr"/>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D238" s="3" t="inlineStr"/>
       <c r="E238" s="3" t="inlineStr"/>
       <c r="F238" s="3" t="inlineStr"/>
@@ -9765,7 +9777,7 @@
       </c>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D256" s="6" t="n">
         <v>99</v>

--- a/DCAT/dcat_profile_coverage.xlsx
+++ b/DCAT/dcat_profile_coverage.xlsx
@@ -5032,7 +5032,11 @@
           <t>dcat:Distribution</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr"/>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5460,7 +5464,11 @@
           <t>dcat:Dataset</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr"/>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6656,7 +6664,11 @@
           <t>dqv:QualityMeasurement</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr"/>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D153" s="3" t="inlineStr"/>
       <c r="E153" s="3" t="inlineStr"/>
       <c r="F153" s="3" t="inlineStr"/>
@@ -7501,10 +7513,14 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>dcat:Distribution</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr"/>
+          <t>dcat:Dataset</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D180" s="3" t="inlineStr"/>
       <c r="E180" s="4" t="inlineStr">
         <is>
@@ -9088,7 +9104,11 @@
           <t>odrl:Policy</t>
         </is>
       </c>
-      <c r="C232" s="2" t="inlineStr"/>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D232" s="3" t="inlineStr"/>
       <c r="E232" s="3" t="inlineStr"/>
       <c r="F232" s="3" t="inlineStr"/>
@@ -9116,7 +9136,11 @@
           <t>odrl:Policy</t>
         </is>
       </c>
-      <c r="C233" s="2" t="inlineStr"/>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D233" s="3" t="inlineStr"/>
       <c r="E233" s="3" t="inlineStr"/>
       <c r="F233" s="3" t="inlineStr"/>
@@ -9144,7 +9168,11 @@
           <t>odrl:Policy</t>
         </is>
       </c>
-      <c r="C234" s="2" t="inlineStr"/>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D234" s="3" t="inlineStr"/>
       <c r="E234" s="3" t="inlineStr"/>
       <c r="F234" s="3" t="inlineStr"/>
@@ -9172,7 +9200,11 @@
           <t>odrl:Rule</t>
         </is>
       </c>
-      <c r="C235" s="2" t="inlineStr"/>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D235" s="3" t="inlineStr"/>
       <c r="E235" s="3" t="inlineStr"/>
       <c r="F235" s="3" t="inlineStr"/>
@@ -9520,7 +9552,11 @@
           <t>dqv:QualityMeasurement</t>
         </is>
       </c>
-      <c r="C247" s="2" t="inlineStr"/>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr"/>
       <c r="F247" s="3" t="inlineStr"/>
@@ -9777,7 +9813,7 @@
       </c>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="D256" s="6" t="n">
         <v>99</v>
@@ -10673,7 +10709,7 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-10</t>
+          <t>Generated: 2026-09-11</t>
         </is>
       </c>
     </row>
